--- a/artfynd/A 19851-2022 artfynd.xlsx
+++ b/artfynd/A 19851-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19851-2022 artfynd.xlsx
+++ b/artfynd/A 19851-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97187073</v>
+        <v>97187071</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541891.8391193884</v>
+        <v>541949</v>
       </c>
       <c r="R2" t="n">
-        <v>7036629.87856347</v>
+        <v>7036688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +743,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97187071</v>
+        <v>97187067</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541948.8523454062</v>
+        <v>542101</v>
       </c>
       <c r="R3" t="n">
-        <v>7036688.783268379</v>
+        <v>7036735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +844,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97187069</v>
+        <v>97187070</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541965.6659045117</v>
+        <v>541955</v>
       </c>
       <c r="R4" t="n">
-        <v>7036704.661465215</v>
+        <v>7036697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +945,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97187070</v>
+        <v>97187072</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1067,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541955.0227079934</v>
+        <v>541887</v>
       </c>
       <c r="R5" t="n">
-        <v>7036696.469304045</v>
+        <v>7036628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1046,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97187072</v>
+        <v>97187073</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1090,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541887.8198927813</v>
+        <v>541891</v>
       </c>
       <c r="R6" t="n">
-        <v>7036628.931118</v>
+        <v>7036630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,37 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97187067</v>
+        <v>97187068</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542100.0926750113</v>
+        <v>542037</v>
       </c>
       <c r="R7" t="n">
-        <v>7036735.508618399</v>
+        <v>7036744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,19 +1252,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,6 +1278,107 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97187069</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Borgvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>541966</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7036705</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 19851-2022 artfynd.xlsx
+++ b/artfynd/A 19851-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187071</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187067</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187072</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187073</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,8 +1418,22 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97187069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>